--- a/Budgeting System_CC-GL.xlsx
+++ b/Budgeting System_CC-GL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jumalonpvp\Downloads\Budgeting System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B574BC-3411-488D-B147-A02BA7715B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA94AEAB-852D-4F03-A4A8-FEB39B4D6927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{E44E2058-07CC-4880-BE5F-4811E07EFFAA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E44E2058-07CC-4880-BE5F-4811E07EFFAA}"/>
   </bookViews>
   <sheets>
     <sheet name="GL" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CC!$A$1:$E$543</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GL!$A$1:$C$504</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GL!$A$1:$C$505</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2514" uniqueCount="855">
   <si>
     <t>Name</t>
   </si>
@@ -2572,15 +2572,6 @@
     <t>Other Inc. - Others</t>
   </si>
   <si>
-    <t>Classification</t>
-  </si>
-  <si>
-    <t>Depreciation, Amortization &amp; Interest Expense</t>
-  </si>
-  <si>
-    <t>Revenue and Cost of Sales</t>
-  </si>
-  <si>
     <t>Commission</t>
   </si>
   <si>
@@ -2606,6 +2597,18 @@
   </si>
   <si>
     <t>Cost Center</t>
+  </si>
+  <si>
+    <t>Revenue &amp; Cost of Sales</t>
+  </si>
+  <si>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Depreciation &amp; Amortization</t>
+  </si>
+  <si>
+    <t>Financial Scope</t>
   </si>
 </sst>
 </file>
@@ -3009,7 +3012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5820EA-EB21-4A41-8285-BAA1AA34B157}">
-  <dimension ref="A1:C504"/>
+  <dimension ref="A1:C505"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.7265625" bestFit="1" customWidth="1"/>
@@ -3025,7 +3028,7 @@
         <v>312</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -3036,7 +3039,7 @@
         <v>313</v>
       </c>
       <c r="C2" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -3047,7 +3050,7 @@
         <v>314</v>
       </c>
       <c r="C3" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -3058,7 +3061,7 @@
         <v>315</v>
       </c>
       <c r="C4" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -3069,7 +3072,7 @@
         <v>316</v>
       </c>
       <c r="C5" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -3080,7 +3083,7 @@
         <v>317</v>
       </c>
       <c r="C6" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -3091,7 +3094,7 @@
         <v>318</v>
       </c>
       <c r="C7" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -3102,7 +3105,7 @@
         <v>319</v>
       </c>
       <c r="C8" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -3113,7 +3116,7 @@
         <v>320</v>
       </c>
       <c r="C9" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -3124,7 +3127,7 @@
         <v>321</v>
       </c>
       <c r="C10" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -3135,7 +3138,7 @@
         <v>322</v>
       </c>
       <c r="C11" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -3146,7 +3149,7 @@
         <v>323</v>
       </c>
       <c r="C12" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -3157,7 +3160,7 @@
         <v>324</v>
       </c>
       <c r="C13" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -3168,7 +3171,7 @@
         <v>325</v>
       </c>
       <c r="C14" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -3179,7 +3182,7 @@
         <v>326</v>
       </c>
       <c r="C15" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -3190,7 +3193,7 @@
         <v>327</v>
       </c>
       <c r="C16" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -3201,7 +3204,7 @@
         <v>328</v>
       </c>
       <c r="C17" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -3212,7 +3215,7 @@
         <v>329</v>
       </c>
       <c r="C18" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -3223,7 +3226,7 @@
         <v>330</v>
       </c>
       <c r="C19" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -3234,7 +3237,7 @@
         <v>331</v>
       </c>
       <c r="C20" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -3245,7 +3248,7 @@
         <v>332</v>
       </c>
       <c r="C21" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -3256,7 +3259,7 @@
         <v>333</v>
       </c>
       <c r="C22" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -3267,7 +3270,7 @@
         <v>334</v>
       </c>
       <c r="C23" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -3278,7 +3281,7 @@
         <v>335</v>
       </c>
       <c r="C24" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -3289,7 +3292,7 @@
         <v>336</v>
       </c>
       <c r="C25" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -3300,7 +3303,7 @@
         <v>337</v>
       </c>
       <c r="C26" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -3311,7 +3314,7 @@
         <v>338</v>
       </c>
       <c r="C27" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -3322,7 +3325,7 @@
         <v>339</v>
       </c>
       <c r="C28" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -3333,7 +3336,7 @@
         <v>340</v>
       </c>
       <c r="C29" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -3344,7 +3347,7 @@
         <v>341</v>
       </c>
       <c r="C30" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -3355,7 +3358,7 @@
         <v>342</v>
       </c>
       <c r="C31" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -3366,7 +3369,7 @@
         <v>343</v>
       </c>
       <c r="C32" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -3377,7 +3380,7 @@
         <v>344</v>
       </c>
       <c r="C33" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -3388,7 +3391,7 @@
         <v>345</v>
       </c>
       <c r="C34" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -3399,7 +3402,7 @@
         <v>346</v>
       </c>
       <c r="C35" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
@@ -3410,7 +3413,7 @@
         <v>347</v>
       </c>
       <c r="C36" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -3421,7 +3424,7 @@
         <v>348</v>
       </c>
       <c r="C37" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
@@ -3432,7 +3435,7 @@
         <v>349</v>
       </c>
       <c r="C38" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
@@ -3443,7 +3446,7 @@
         <v>350</v>
       </c>
       <c r="C39" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
@@ -3454,7 +3457,7 @@
         <v>351</v>
       </c>
       <c r="C40" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
@@ -3465,7 +3468,7 @@
         <v>352</v>
       </c>
       <c r="C41" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -3476,7 +3479,7 @@
         <v>353</v>
       </c>
       <c r="C42" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
@@ -3487,7 +3490,7 @@
         <v>354</v>
       </c>
       <c r="C43" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
@@ -3498,7 +3501,7 @@
         <v>355</v>
       </c>
       <c r="C44" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
@@ -3509,7 +3512,7 @@
         <v>356</v>
       </c>
       <c r="C45" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
@@ -3520,7 +3523,7 @@
         <v>357</v>
       </c>
       <c r="C46" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -3531,7 +3534,7 @@
         <v>358</v>
       </c>
       <c r="C47" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
@@ -3542,7 +3545,7 @@
         <v>359</v>
       </c>
       <c r="C48" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
@@ -3553,7 +3556,7 @@
         <v>360</v>
       </c>
       <c r="C49" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
@@ -3564,7 +3567,7 @@
         <v>361</v>
       </c>
       <c r="C50" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
@@ -3575,7 +3578,7 @@
         <v>362</v>
       </c>
       <c r="C51" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
@@ -3586,7 +3589,7 @@
         <v>363</v>
       </c>
       <c r="C52" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
@@ -3597,7 +3600,7 @@
         <v>364</v>
       </c>
       <c r="C53" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
@@ -3608,7 +3611,7 @@
         <v>365</v>
       </c>
       <c r="C54" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -3619,7 +3622,7 @@
         <v>366</v>
       </c>
       <c r="C55" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -3630,7 +3633,7 @@
         <v>367</v>
       </c>
       <c r="C56" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
@@ -3641,7 +3644,7 @@
         <v>368</v>
       </c>
       <c r="C57" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -3652,7 +3655,7 @@
         <v>369</v>
       </c>
       <c r="C58" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -3663,7 +3666,7 @@
         <v>370</v>
       </c>
       <c r="C59" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
@@ -3674,7 +3677,7 @@
         <v>371</v>
       </c>
       <c r="C60" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
@@ -3685,7 +3688,7 @@
         <v>372</v>
       </c>
       <c r="C61" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
@@ -3696,7 +3699,7 @@
         <v>373</v>
       </c>
       <c r="C62" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
@@ -3707,7 +3710,7 @@
         <v>374</v>
       </c>
       <c r="C63" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
@@ -3718,7 +3721,7 @@
         <v>375</v>
       </c>
       <c r="C64" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -3729,7 +3732,7 @@
         <v>376</v>
       </c>
       <c r="C65" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
@@ -3740,7 +3743,7 @@
         <v>377</v>
       </c>
       <c r="C66" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -3751,7 +3754,7 @@
         <v>378</v>
       </c>
       <c r="C67" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
@@ -3762,7 +3765,7 @@
         <v>379</v>
       </c>
       <c r="C68" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
@@ -3773,7 +3776,7 @@
         <v>380</v>
       </c>
       <c r="C69" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
@@ -3784,7 +3787,7 @@
         <v>381</v>
       </c>
       <c r="C70" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -3795,7 +3798,7 @@
         <v>382</v>
       </c>
       <c r="C71" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
@@ -3806,7 +3809,7 @@
         <v>383</v>
       </c>
       <c r="C72" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
@@ -3817,7 +3820,7 @@
         <v>384</v>
       </c>
       <c r="C73" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
@@ -3828,7 +3831,7 @@
         <v>385</v>
       </c>
       <c r="C74" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
@@ -3839,7 +3842,7 @@
         <v>386</v>
       </c>
       <c r="C75" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
@@ -3850,7 +3853,7 @@
         <v>387</v>
       </c>
       <c r="C76" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
@@ -3861,7 +3864,7 @@
         <v>388</v>
       </c>
       <c r="C77" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
@@ -3872,7 +3875,7 @@
         <v>389</v>
       </c>
       <c r="C78" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
@@ -3883,7 +3886,7 @@
         <v>390</v>
       </c>
       <c r="C79" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
@@ -3894,7 +3897,7 @@
         <v>391</v>
       </c>
       <c r="C80" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
@@ -3905,7 +3908,7 @@
         <v>392</v>
       </c>
       <c r="C81" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
@@ -3916,7 +3919,7 @@
         <v>393</v>
       </c>
       <c r="C82" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
@@ -3927,7 +3930,7 @@
         <v>394</v>
       </c>
       <c r="C83" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
@@ -3938,7 +3941,7 @@
         <v>395</v>
       </c>
       <c r="C84" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
@@ -3949,7 +3952,7 @@
         <v>396</v>
       </c>
       <c r="C85" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
@@ -3960,7 +3963,7 @@
         <v>397</v>
       </c>
       <c r="C86" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
@@ -3971,7 +3974,7 @@
         <v>398</v>
       </c>
       <c r="C87" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
@@ -3982,7 +3985,7 @@
         <v>399</v>
       </c>
       <c r="C88" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
@@ -3993,7 +3996,7 @@
         <v>400</v>
       </c>
       <c r="C89" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
@@ -4004,7 +4007,7 @@
         <v>401</v>
       </c>
       <c r="C90" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
@@ -4015,7 +4018,7 @@
         <v>402</v>
       </c>
       <c r="C91" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
@@ -4026,7 +4029,7 @@
         <v>403</v>
       </c>
       <c r="C92" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
@@ -4037,7 +4040,7 @@
         <v>404</v>
       </c>
       <c r="C93" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
@@ -4048,7 +4051,7 @@
         <v>405</v>
       </c>
       <c r="C94" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
@@ -4059,7 +4062,7 @@
         <v>406</v>
       </c>
       <c r="C95" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
@@ -4070,7 +4073,7 @@
         <v>407</v>
       </c>
       <c r="C96" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
@@ -4081,7 +4084,7 @@
         <v>408</v>
       </c>
       <c r="C97" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
@@ -4092,7 +4095,7 @@
         <v>409</v>
       </c>
       <c r="C98" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
@@ -4103,7 +4106,7 @@
         <v>410</v>
       </c>
       <c r="C99" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
@@ -4114,7 +4117,7 @@
         <v>411</v>
       </c>
       <c r="C100" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
@@ -4125,7 +4128,7 @@
         <v>412</v>
       </c>
       <c r="C101" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
@@ -4136,7 +4139,7 @@
         <v>413</v>
       </c>
       <c r="C102" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
@@ -4147,7 +4150,7 @@
         <v>414</v>
       </c>
       <c r="C103" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
@@ -4158,7 +4161,7 @@
         <v>415</v>
       </c>
       <c r="C104" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
@@ -4169,7 +4172,7 @@
         <v>416</v>
       </c>
       <c r="C105" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
@@ -4180,7 +4183,7 @@
         <v>417</v>
       </c>
       <c r="C106" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
@@ -4191,7 +4194,7 @@
         <v>418</v>
       </c>
       <c r="C107" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
@@ -4202,7 +4205,7 @@
         <v>419</v>
       </c>
       <c r="C108" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
@@ -4213,7 +4216,7 @@
         <v>420</v>
       </c>
       <c r="C109" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
@@ -4224,7 +4227,7 @@
         <v>421</v>
       </c>
       <c r="C110" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
@@ -4235,7 +4238,7 @@
         <v>422</v>
       </c>
       <c r="C111" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
@@ -4246,7 +4249,7 @@
         <v>423</v>
       </c>
       <c r="C112" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
@@ -4257,7 +4260,7 @@
         <v>424</v>
       </c>
       <c r="C113" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
@@ -4268,7 +4271,7 @@
         <v>425</v>
       </c>
       <c r="C114" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
@@ -4279,7 +4282,7 @@
         <v>426</v>
       </c>
       <c r="C115" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
@@ -4290,7 +4293,7 @@
         <v>427</v>
       </c>
       <c r="C116" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
@@ -4301,7 +4304,7 @@
         <v>428</v>
       </c>
       <c r="C117" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
@@ -4312,7 +4315,7 @@
         <v>429</v>
       </c>
       <c r="C118" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
@@ -4323,7 +4326,7 @@
         <v>430</v>
       </c>
       <c r="C119" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
@@ -4334,7 +4337,7 @@
         <v>431</v>
       </c>
       <c r="C120" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
@@ -4345,7 +4348,7 @@
         <v>432</v>
       </c>
       <c r="C121" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
@@ -4356,7 +4359,7 @@
         <v>433</v>
       </c>
       <c r="C122" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
@@ -4367,7 +4370,7 @@
         <v>434</v>
       </c>
       <c r="C123" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
@@ -4378,7 +4381,7 @@
         <v>435</v>
       </c>
       <c r="C124" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
@@ -4389,7 +4392,7 @@
         <v>436</v>
       </c>
       <c r="C125" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
@@ -4400,7 +4403,7 @@
         <v>437</v>
       </c>
       <c r="C126" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
@@ -4411,7 +4414,7 @@
         <v>438</v>
       </c>
       <c r="C127" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
@@ -4422,7 +4425,7 @@
         <v>439</v>
       </c>
       <c r="C128" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
@@ -4433,7 +4436,7 @@
         <v>440</v>
       </c>
       <c r="C129" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
@@ -4444,7 +4447,7 @@
         <v>441</v>
       </c>
       <c r="C130" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
@@ -4455,7 +4458,7 @@
         <v>442</v>
       </c>
       <c r="C131" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
@@ -4466,7 +4469,7 @@
         <v>443</v>
       </c>
       <c r="C132" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
@@ -4477,7 +4480,7 @@
         <v>444</v>
       </c>
       <c r="C133" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
@@ -4488,7 +4491,7 @@
         <v>445</v>
       </c>
       <c r="C134" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
@@ -4499,7 +4502,7 @@
         <v>446</v>
       </c>
       <c r="C135" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
@@ -4510,7 +4513,7 @@
         <v>447</v>
       </c>
       <c r="C136" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
@@ -4521,7 +4524,7 @@
         <v>448</v>
       </c>
       <c r="C137" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
@@ -4532,7 +4535,7 @@
         <v>449</v>
       </c>
       <c r="C138" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
@@ -4543,7 +4546,7 @@
         <v>450</v>
       </c>
       <c r="C139" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
@@ -4554,7 +4557,7 @@
         <v>451</v>
       </c>
       <c r="C140" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
@@ -4565,7 +4568,7 @@
         <v>452</v>
       </c>
       <c r="C141" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
@@ -4576,7 +4579,7 @@
         <v>453</v>
       </c>
       <c r="C142" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
@@ -4587,7 +4590,7 @@
         <v>454</v>
       </c>
       <c r="C143" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
@@ -4598,7 +4601,7 @@
         <v>455</v>
       </c>
       <c r="C144" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
@@ -4609,7 +4612,7 @@
         <v>456</v>
       </c>
       <c r="C145" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
@@ -4620,7 +4623,7 @@
         <v>457</v>
       </c>
       <c r="C146" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
@@ -4631,7 +4634,7 @@
         <v>458</v>
       </c>
       <c r="C147" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
@@ -4642,7 +4645,7 @@
         <v>459</v>
       </c>
       <c r="C148" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
@@ -4653,7 +4656,7 @@
         <v>460</v>
       </c>
       <c r="C149" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -4664,7 +4667,7 @@
         <v>461</v>
       </c>
       <c r="C150" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -4675,7 +4678,7 @@
         <v>462</v>
       </c>
       <c r="C151" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
@@ -4686,7 +4689,7 @@
         <v>463</v>
       </c>
       <c r="C152" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
@@ -4697,7 +4700,7 @@
         <v>464</v>
       </c>
       <c r="C153" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
@@ -4708,7 +4711,7 @@
         <v>465</v>
       </c>
       <c r="C154" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
@@ -4719,7 +4722,7 @@
         <v>466</v>
       </c>
       <c r="C155" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
@@ -4730,7 +4733,7 @@
         <v>467</v>
       </c>
       <c r="C156" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
@@ -4741,7 +4744,7 @@
         <v>468</v>
       </c>
       <c r="C157" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
@@ -4752,7 +4755,7 @@
         <v>469</v>
       </c>
       <c r="C158" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
@@ -4763,7 +4766,7 @@
         <v>470</v>
       </c>
       <c r="C159" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
@@ -4774,7 +4777,7 @@
         <v>471</v>
       </c>
       <c r="C160" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
@@ -4785,7 +4788,7 @@
         <v>472</v>
       </c>
       <c r="C161" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
@@ -4796,7 +4799,7 @@
         <v>473</v>
       </c>
       <c r="C162" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
@@ -4807,7 +4810,7 @@
         <v>474</v>
       </c>
       <c r="C163" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
@@ -4818,7 +4821,7 @@
         <v>475</v>
       </c>
       <c r="C164" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
@@ -4829,7 +4832,7 @@
         <v>476</v>
       </c>
       <c r="C165" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
@@ -4840,7 +4843,7 @@
         <v>477</v>
       </c>
       <c r="C166" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
@@ -4851,7 +4854,7 @@
         <v>478</v>
       </c>
       <c r="C167" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
@@ -4862,7 +4865,7 @@
         <v>479</v>
       </c>
       <c r="C168" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
@@ -4873,7 +4876,7 @@
         <v>480</v>
       </c>
       <c r="C169" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
@@ -4884,7 +4887,7 @@
         <v>481</v>
       </c>
       <c r="C170" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
@@ -4895,7 +4898,7 @@
         <v>482</v>
       </c>
       <c r="C171" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
@@ -4906,7 +4909,7 @@
         <v>483</v>
       </c>
       <c r="C172" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
@@ -4917,7 +4920,7 @@
         <v>484</v>
       </c>
       <c r="C173" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
@@ -4928,7 +4931,7 @@
         <v>485</v>
       </c>
       <c r="C174" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
@@ -4939,7 +4942,7 @@
         <v>486</v>
       </c>
       <c r="C175" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
@@ -4950,7 +4953,7 @@
         <v>487</v>
       </c>
       <c r="C176" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
@@ -4961,7 +4964,7 @@
         <v>488</v>
       </c>
       <c r="C177" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
@@ -4972,7 +4975,7 @@
         <v>489</v>
       </c>
       <c r="C178" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
@@ -4983,7 +4986,7 @@
         <v>490</v>
       </c>
       <c r="C179" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
@@ -4994,7 +4997,7 @@
         <v>491</v>
       </c>
       <c r="C180" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
@@ -5005,7 +5008,7 @@
         <v>492</v>
       </c>
       <c r="C181" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
@@ -5016,7 +5019,7 @@
         <v>482</v>
       </c>
       <c r="C182" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
@@ -5027,7 +5030,7 @@
         <v>493</v>
       </c>
       <c r="C183" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
@@ -5038,7 +5041,7 @@
         <v>494</v>
       </c>
       <c r="C184" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
@@ -5049,7 +5052,7 @@
         <v>495</v>
       </c>
       <c r="C185" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
@@ -5060,7 +5063,7 @@
         <v>496</v>
       </c>
       <c r="C186" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
@@ -5071,7 +5074,7 @@
         <v>497</v>
       </c>
       <c r="C187" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
@@ -5082,7 +5085,7 @@
         <v>498</v>
       </c>
       <c r="C188" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
@@ -5093,7 +5096,7 @@
         <v>499</v>
       </c>
       <c r="C189" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
@@ -5104,7 +5107,7 @@
         <v>500</v>
       </c>
       <c r="C190" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
@@ -5115,7 +5118,7 @@
         <v>501</v>
       </c>
       <c r="C191" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
@@ -5126,7 +5129,7 @@
         <v>502</v>
       </c>
       <c r="C192" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
@@ -5137,7 +5140,7 @@
         <v>503</v>
       </c>
       <c r="C193" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
@@ -5148,7 +5151,7 @@
         <v>504</v>
       </c>
       <c r="C194" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
@@ -5159,7 +5162,7 @@
         <v>505</v>
       </c>
       <c r="C195" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
@@ -5170,7 +5173,7 @@
         <v>506</v>
       </c>
       <c r="C196" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
@@ -5181,7 +5184,7 @@
         <v>507</v>
       </c>
       <c r="C197" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
@@ -5192,7 +5195,7 @@
         <v>508</v>
       </c>
       <c r="C198" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
@@ -5203,7 +5206,7 @@
         <v>509</v>
       </c>
       <c r="C199" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
@@ -5214,7 +5217,7 @@
         <v>510</v>
       </c>
       <c r="C200" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
@@ -5225,7 +5228,7 @@
         <v>511</v>
       </c>
       <c r="C201" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
@@ -5236,7 +5239,7 @@
         <v>512</v>
       </c>
       <c r="C202" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
@@ -5247,7 +5250,7 @@
         <v>513</v>
       </c>
       <c r="C203" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
@@ -5258,7 +5261,7 @@
         <v>514</v>
       </c>
       <c r="C204" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
@@ -5269,7 +5272,7 @@
         <v>515</v>
       </c>
       <c r="C205" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
@@ -5280,7 +5283,7 @@
         <v>516</v>
       </c>
       <c r="C206" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
@@ -5291,7 +5294,7 @@
         <v>517</v>
       </c>
       <c r="C207" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
@@ -5302,7 +5305,7 @@
         <v>518</v>
       </c>
       <c r="C208" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
@@ -5313,7 +5316,7 @@
         <v>519</v>
       </c>
       <c r="C209" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
@@ -5324,7 +5327,7 @@
         <v>520</v>
       </c>
       <c r="C210" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
@@ -5335,7 +5338,7 @@
         <v>521</v>
       </c>
       <c r="C211" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
@@ -5346,7 +5349,7 @@
         <v>522</v>
       </c>
       <c r="C212" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
@@ -5357,7 +5360,7 @@
         <v>523</v>
       </c>
       <c r="C213" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
@@ -5368,7 +5371,7 @@
         <v>524</v>
       </c>
       <c r="C214" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
@@ -5379,7 +5382,7 @@
         <v>525</v>
       </c>
       <c r="C215" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
@@ -5390,7 +5393,7 @@
         <v>526</v>
       </c>
       <c r="C216" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
@@ -5401,7 +5404,7 @@
         <v>527</v>
       </c>
       <c r="C217" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
@@ -5412,7 +5415,7 @@
         <v>528</v>
       </c>
       <c r="C218" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
@@ -5423,7 +5426,7 @@
         <v>529</v>
       </c>
       <c r="C219" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
@@ -5434,7 +5437,7 @@
         <v>530</v>
       </c>
       <c r="C220" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
@@ -5445,7 +5448,7 @@
         <v>531</v>
       </c>
       <c r="C221" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
@@ -5456,7 +5459,7 @@
         <v>532</v>
       </c>
       <c r="C222" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
@@ -5467,7 +5470,7 @@
         <v>533</v>
       </c>
       <c r="C223" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
@@ -5478,7 +5481,7 @@
         <v>534</v>
       </c>
       <c r="C224" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
@@ -5489,7 +5492,7 @@
         <v>535</v>
       </c>
       <c r="C225" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
@@ -5500,7 +5503,7 @@
         <v>536</v>
       </c>
       <c r="C226" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
@@ -5511,7 +5514,7 @@
         <v>537</v>
       </c>
       <c r="C227" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
@@ -5522,7 +5525,7 @@
         <v>538</v>
       </c>
       <c r="C228" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
@@ -5533,7 +5536,7 @@
         <v>539</v>
       </c>
       <c r="C229" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
@@ -5544,7 +5547,7 @@
         <v>540</v>
       </c>
       <c r="C230" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
@@ -5555,7 +5558,7 @@
         <v>541</v>
       </c>
       <c r="C231" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
@@ -5566,7 +5569,7 @@
         <v>542</v>
       </c>
       <c r="C232" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
@@ -5577,7 +5580,7 @@
         <v>543</v>
       </c>
       <c r="C233" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
@@ -5588,7 +5591,7 @@
         <v>544</v>
       </c>
       <c r="C234" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
@@ -5599,7 +5602,7 @@
         <v>545</v>
       </c>
       <c r="C235" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
@@ -5610,7 +5613,7 @@
         <v>546</v>
       </c>
       <c r="C236" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
@@ -5621,7 +5624,7 @@
         <v>547</v>
       </c>
       <c r="C237" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
@@ -5632,7 +5635,7 @@
         <v>548</v>
       </c>
       <c r="C238" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
@@ -5643,7 +5646,7 @@
         <v>549</v>
       </c>
       <c r="C239" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
@@ -5654,7 +5657,7 @@
         <v>550</v>
       </c>
       <c r="C240" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
@@ -5665,7 +5668,7 @@
         <v>551</v>
       </c>
       <c r="C241" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
@@ -5676,7 +5679,7 @@
         <v>552</v>
       </c>
       <c r="C242" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
@@ -5687,7 +5690,7 @@
         <v>553</v>
       </c>
       <c r="C243" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
@@ -5698,7 +5701,7 @@
         <v>554</v>
       </c>
       <c r="C244" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
@@ -5709,7 +5712,7 @@
         <v>555</v>
       </c>
       <c r="C245" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
@@ -5720,7 +5723,7 @@
         <v>556</v>
       </c>
       <c r="C246" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
@@ -5731,7 +5734,7 @@
         <v>557</v>
       </c>
       <c r="C247" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
@@ -5742,7 +5745,7 @@
         <v>558</v>
       </c>
       <c r="C248" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
@@ -5753,7 +5756,7 @@
         <v>559</v>
       </c>
       <c r="C249" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
@@ -5764,7 +5767,7 @@
         <v>560</v>
       </c>
       <c r="C250" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
@@ -5775,7 +5778,7 @@
         <v>561</v>
       </c>
       <c r="C251" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
@@ -5786,7 +5789,7 @@
         <v>562</v>
       </c>
       <c r="C252" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
@@ -5797,7 +5800,7 @@
         <v>563</v>
       </c>
       <c r="C253" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
@@ -5808,7 +5811,7 @@
         <v>564</v>
       </c>
       <c r="C254" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
@@ -5819,7 +5822,7 @@
         <v>565</v>
       </c>
       <c r="C255" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
@@ -5830,7 +5833,7 @@
         <v>566</v>
       </c>
       <c r="C256" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
@@ -5841,7 +5844,7 @@
         <v>567</v>
       </c>
       <c r="C257" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
@@ -5852,7 +5855,7 @@
         <v>568</v>
       </c>
       <c r="C258" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
@@ -5863,7 +5866,7 @@
         <v>569</v>
       </c>
       <c r="C259" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
@@ -5874,7 +5877,7 @@
         <v>570</v>
       </c>
       <c r="C260" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
@@ -5885,7 +5888,7 @@
         <v>571</v>
       </c>
       <c r="C261" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
@@ -5896,7 +5899,7 @@
         <v>572</v>
       </c>
       <c r="C262" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
@@ -5907,7 +5910,7 @@
         <v>573</v>
       </c>
       <c r="C263" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
@@ -5918,7 +5921,7 @@
         <v>574</v>
       </c>
       <c r="C264" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
@@ -5929,7 +5932,7 @@
         <v>575</v>
       </c>
       <c r="C265" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
@@ -5940,7 +5943,7 @@
         <v>576</v>
       </c>
       <c r="C266" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
@@ -5951,7 +5954,7 @@
         <v>577</v>
       </c>
       <c r="C267" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
@@ -5962,7 +5965,7 @@
         <v>578</v>
       </c>
       <c r="C268" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
@@ -5973,7 +5976,7 @@
         <v>579</v>
       </c>
       <c r="C269" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
@@ -5984,7 +5987,7 @@
         <v>580</v>
       </c>
       <c r="C270" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
@@ -5995,7 +5998,7 @@
         <v>581</v>
       </c>
       <c r="C271" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
@@ -6006,7 +6009,7 @@
         <v>582</v>
       </c>
       <c r="C272" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
@@ -6017,7 +6020,7 @@
         <v>583</v>
       </c>
       <c r="C273" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
@@ -6028,7 +6031,7 @@
         <v>584</v>
       </c>
       <c r="C274" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
@@ -6039,7 +6042,7 @@
         <v>585</v>
       </c>
       <c r="C275" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
@@ -6050,7 +6053,7 @@
         <v>586</v>
       </c>
       <c r="C276" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
@@ -6061,7 +6064,7 @@
         <v>587</v>
       </c>
       <c r="C277" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
@@ -6072,7 +6075,7 @@
         <v>588</v>
       </c>
       <c r="C278" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
@@ -6083,7 +6086,7 @@
         <v>589</v>
       </c>
       <c r="C279" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
@@ -6094,7 +6097,7 @@
         <v>590</v>
       </c>
       <c r="C280" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
@@ -6105,7 +6108,7 @@
         <v>591</v>
       </c>
       <c r="C281" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
@@ -6116,7 +6119,7 @@
         <v>592</v>
       </c>
       <c r="C282" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
@@ -6127,7 +6130,7 @@
         <v>593</v>
       </c>
       <c r="C283" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
@@ -6138,7 +6141,7 @@
         <v>594</v>
       </c>
       <c r="C284" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
@@ -6149,7 +6152,7 @@
         <v>595</v>
       </c>
       <c r="C285" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
@@ -6160,7 +6163,7 @@
         <v>596</v>
       </c>
       <c r="C286" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
@@ -6171,7 +6174,7 @@
         <v>597</v>
       </c>
       <c r="C287" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
@@ -6182,7 +6185,7 @@
         <v>598</v>
       </c>
       <c r="C288" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
@@ -6193,7 +6196,7 @@
         <v>599</v>
       </c>
       <c r="C289" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
@@ -6204,7 +6207,7 @@
         <v>600</v>
       </c>
       <c r="C290" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
@@ -6215,7 +6218,7 @@
         <v>601</v>
       </c>
       <c r="C291" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
@@ -6226,7 +6229,7 @@
         <v>602</v>
       </c>
       <c r="C292" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
@@ -6237,7 +6240,7 @@
         <v>603</v>
       </c>
       <c r="C293" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
@@ -6248,7 +6251,7 @@
         <v>604</v>
       </c>
       <c r="C294" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
@@ -6259,7 +6262,7 @@
         <v>605</v>
       </c>
       <c r="C295" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
@@ -6270,7 +6273,7 @@
         <v>606</v>
       </c>
       <c r="C296" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
@@ -6281,7 +6284,7 @@
         <v>607</v>
       </c>
       <c r="C297" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
@@ -6292,7 +6295,7 @@
         <v>608</v>
       </c>
       <c r="C298" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
@@ -6303,7 +6306,7 @@
         <v>609</v>
       </c>
       <c r="C299" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
@@ -6314,7 +6317,7 @@
         <v>610</v>
       </c>
       <c r="C300" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
@@ -6325,7 +6328,7 @@
         <v>611</v>
       </c>
       <c r="C301" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
@@ -6336,7 +6339,7 @@
         <v>612</v>
       </c>
       <c r="C302" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
@@ -6347,7 +6350,7 @@
         <v>613</v>
       </c>
       <c r="C303" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
@@ -6358,7 +6361,7 @@
         <v>614</v>
       </c>
       <c r="C304" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
@@ -6369,7 +6372,7 @@
         <v>615</v>
       </c>
       <c r="C305" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
@@ -6380,7 +6383,7 @@
         <v>616</v>
       </c>
       <c r="C306" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
@@ -6391,7 +6394,7 @@
         <v>617</v>
       </c>
       <c r="C307" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
@@ -6402,7 +6405,7 @@
         <v>618</v>
       </c>
       <c r="C308" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
@@ -6413,7 +6416,7 @@
         <v>619</v>
       </c>
       <c r="C309" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
@@ -6424,7 +6427,7 @@
         <v>620</v>
       </c>
       <c r="C310" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
@@ -6435,7 +6438,7 @@
         <v>621</v>
       </c>
       <c r="C311" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
@@ -6446,7 +6449,7 @@
         <v>622</v>
       </c>
       <c r="C312" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
@@ -6457,7 +6460,7 @@
         <v>623</v>
       </c>
       <c r="C313" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
@@ -6468,7 +6471,7 @@
         <v>624</v>
       </c>
       <c r="C314" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
@@ -6479,7 +6482,7 @@
         <v>625</v>
       </c>
       <c r="C315" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
@@ -6490,7 +6493,7 @@
         <v>626</v>
       </c>
       <c r="C316" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
@@ -6501,7 +6504,7 @@
         <v>627</v>
       </c>
       <c r="C317" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
@@ -6512,7 +6515,7 @@
         <v>628</v>
       </c>
       <c r="C318" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
@@ -6523,7 +6526,7 @@
         <v>629</v>
       </c>
       <c r="C319" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
@@ -6534,7 +6537,7 @@
         <v>630</v>
       </c>
       <c r="C320" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
@@ -6545,7 +6548,7 @@
         <v>631</v>
       </c>
       <c r="C321" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
@@ -6556,7 +6559,7 @@
         <v>632</v>
       </c>
       <c r="C322" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
@@ -6567,7 +6570,7 @@
         <v>633</v>
       </c>
       <c r="C323" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
@@ -6578,7 +6581,7 @@
         <v>634</v>
       </c>
       <c r="C324" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
@@ -6589,7 +6592,7 @@
         <v>635</v>
       </c>
       <c r="C325" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
@@ -6600,7 +6603,7 @@
         <v>636</v>
       </c>
       <c r="C326" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
@@ -6611,7 +6614,7 @@
         <v>637</v>
       </c>
       <c r="C327" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
@@ -6622,7 +6625,7 @@
         <v>638</v>
       </c>
       <c r="C328" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.35">
@@ -6633,7 +6636,7 @@
         <v>639</v>
       </c>
       <c r="C329" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
@@ -6644,7 +6647,7 @@
         <v>640</v>
       </c>
       <c r="C330" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
@@ -6655,7 +6658,7 @@
         <v>641</v>
       </c>
       <c r="C331" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
@@ -6666,7 +6669,7 @@
         <v>642</v>
       </c>
       <c r="C332" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.35">
@@ -6677,7 +6680,7 @@
         <v>643</v>
       </c>
       <c r="C333" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
@@ -6688,7 +6691,7 @@
         <v>644</v>
       </c>
       <c r="C334" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.35">
@@ -6699,7 +6702,7 @@
         <v>645</v>
       </c>
       <c r="C335" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.35">
@@ -6710,7 +6713,7 @@
         <v>646</v>
       </c>
       <c r="C336" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
@@ -6721,7 +6724,7 @@
         <v>647</v>
       </c>
       <c r="C337" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
@@ -6732,7 +6735,7 @@
         <v>648</v>
       </c>
       <c r="C338" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
@@ -6743,7 +6746,7 @@
         <v>649</v>
       </c>
       <c r="C339" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
@@ -6754,15 +6757,15 @@
         <v>650</v>
       </c>
       <c r="C340" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A341">
-        <v>61901110</v>
+        <v>61901109</v>
       </c>
       <c r="B341" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C341" t="s">
         <v>843</v>
@@ -6770,197 +6773,197 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A342">
-        <v>61901111</v>
+        <v>61901110</v>
       </c>
       <c r="B342" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C342" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A343">
-        <v>61901112</v>
+        <v>61901111</v>
       </c>
       <c r="B343" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C343" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A344">
-        <v>61959101</v>
+        <v>61901112</v>
       </c>
       <c r="B344" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C344" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A345">
-        <v>61959102</v>
+        <v>61959101</v>
       </c>
       <c r="B345" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C345" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A346">
-        <v>61959103</v>
+        <v>61959102</v>
       </c>
       <c r="B346" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C346" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A347">
-        <v>61959201</v>
+        <v>61959103</v>
       </c>
       <c r="B347" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C347" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A348">
-        <v>61959202</v>
+        <v>61959201</v>
       </c>
       <c r="B348" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C348" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A349">
-        <v>61959994</v>
+        <v>61959202</v>
       </c>
       <c r="B349" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C349" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A350">
-        <v>61959995</v>
+        <v>61959994</v>
       </c>
       <c r="B350" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C350" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A351">
-        <v>61959996</v>
+        <v>61959995</v>
       </c>
       <c r="B351" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C351" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A352">
-        <v>61959997</v>
+        <v>61959996</v>
       </c>
       <c r="B352" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C352" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A353">
-        <v>61959998</v>
+        <v>61959997</v>
       </c>
       <c r="B353" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C353" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A354">
-        <v>61959999</v>
+        <v>61959998</v>
       </c>
       <c r="B354" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C354" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A355">
-        <v>61961101</v>
+        <v>61959999</v>
       </c>
       <c r="B355" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C355" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A356">
-        <v>61961201</v>
+        <v>61961101</v>
       </c>
       <c r="B356" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C356" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A357">
-        <v>61961301</v>
+        <v>61961201</v>
       </c>
       <c r="B357" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C357" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A358">
-        <v>61961302</v>
+        <v>61961301</v>
       </c>
       <c r="B358" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C358" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A359">
-        <v>62011101</v>
+        <v>61961302</v>
       </c>
       <c r="B359" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C359" t="s">
         <v>843</v>
@@ -6968,1601 +6971,1612 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A360">
-        <v>62011102</v>
+        <v>62011101</v>
       </c>
       <c r="B360" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C360" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A361">
-        <v>62011103</v>
+        <v>62011102</v>
       </c>
       <c r="B361" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C361" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A362">
-        <v>62011104</v>
+        <v>62011103</v>
       </c>
       <c r="B362" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C362" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A363">
-        <v>62011901</v>
+        <v>62011104</v>
       </c>
       <c r="B363" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C363" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A364">
-        <v>62011902</v>
+        <v>62011901</v>
       </c>
       <c r="B364" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C364" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A365">
-        <v>62011903</v>
+        <v>62011902</v>
       </c>
       <c r="B365" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C365" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A366">
-        <v>62011904</v>
+        <v>62011903</v>
       </c>
       <c r="B366" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C366" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A367">
-        <v>62011999</v>
+        <v>62011904</v>
       </c>
       <c r="B367" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C367" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A368">
-        <v>68011101</v>
+        <v>62011999</v>
       </c>
       <c r="B368" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C368" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A369">
-        <v>68011102</v>
+        <v>68011101</v>
       </c>
       <c r="B369" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C369" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A370">
-        <v>68011103</v>
+        <v>68011102</v>
       </c>
       <c r="B370" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C370" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A371">
-        <v>69951101</v>
+        <v>68011103</v>
       </c>
       <c r="B371" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C371" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A372">
-        <v>69951201</v>
+        <v>69951101</v>
       </c>
       <c r="B372" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C372" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A373">
-        <v>69951301</v>
+        <v>69951201</v>
       </c>
       <c r="B373" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C373" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A374">
-        <v>69951401</v>
+        <v>69951301</v>
       </c>
       <c r="B374" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C374" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A375">
-        <v>69952101</v>
+        <v>69951401</v>
       </c>
       <c r="B375" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C375" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A376">
-        <v>69959901</v>
+        <v>69952101</v>
       </c>
       <c r="B376" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C376" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A377">
-        <v>69959998</v>
+        <v>69959901</v>
       </c>
       <c r="B377" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C377" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A378">
-        <v>69959999</v>
+        <v>69959998</v>
       </c>
       <c r="B378" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C378" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A379">
-        <v>52121101</v>
+        <v>69959999</v>
       </c>
       <c r="B379" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C379" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A380">
-        <v>52121102</v>
+        <v>52121101</v>
       </c>
       <c r="B380" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C380" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A381">
-        <v>52121103</v>
+        <v>52121102</v>
       </c>
       <c r="B381" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C381" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A382">
-        <v>52121104</v>
+        <v>52121103</v>
       </c>
       <c r="B382" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C382" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A383">
-        <v>52121105</v>
+        <v>52121104</v>
       </c>
       <c r="B383" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C383" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A384">
-        <v>52121106</v>
+        <v>52121105</v>
       </c>
       <c r="B384" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C384" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A385">
-        <v>52121201</v>
+        <v>52121106</v>
       </c>
       <c r="B385" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C385" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A386">
-        <v>52121202</v>
+        <v>52121201</v>
       </c>
       <c r="B386" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C386" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A387">
-        <v>52121203</v>
+        <v>52121202</v>
       </c>
       <c r="B387" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C387" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A388">
-        <v>52121301</v>
+        <v>52121203</v>
       </c>
       <c r="B388" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C388" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A389">
-        <v>52121302</v>
+        <v>52121301</v>
       </c>
       <c r="B389" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C389" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A390">
-        <v>52121303</v>
+        <v>52121302</v>
       </c>
       <c r="B390" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C390" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A391">
-        <v>52121304</v>
+        <v>52121303</v>
       </c>
       <c r="B391" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C391" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A392">
-        <v>52121305</v>
+        <v>52121304</v>
       </c>
       <c r="B392" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C392" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A393">
-        <v>52121306</v>
+        <v>52121305</v>
       </c>
       <c r="B393" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C393" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A394">
-        <v>52121307</v>
+        <v>52121306</v>
       </c>
       <c r="B394" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C394" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A395">
-        <v>52121308</v>
+        <v>52121307</v>
       </c>
       <c r="B395" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C395" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A396">
-        <v>52121309</v>
+        <v>52121308</v>
       </c>
       <c r="B396" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C396" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A397">
-        <v>52121310</v>
+        <v>52121309</v>
       </c>
       <c r="B397" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C397" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A398">
-        <v>52121311</v>
+        <v>52121310</v>
       </c>
       <c r="B398" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C398" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A399">
-        <v>52121312</v>
+        <v>52121311</v>
       </c>
       <c r="B399" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C399" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A400">
-        <v>52121313</v>
+        <v>52121312</v>
       </c>
       <c r="B400" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C400" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A401">
-        <v>52121314</v>
+        <v>52121313</v>
       </c>
       <c r="B401" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C401" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A402">
-        <v>52121315</v>
+        <v>52121314</v>
       </c>
       <c r="B402" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C402" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A403">
-        <v>52121316</v>
+        <v>52121315</v>
       </c>
       <c r="B403" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C403" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A404">
-        <v>52121401</v>
+        <v>52121316</v>
       </c>
       <c r="B404" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C404" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A405">
-        <v>52121402</v>
+        <v>52121401</v>
       </c>
       <c r="B405" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C405" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A406">
-        <v>52121501</v>
+        <v>52121402</v>
       </c>
       <c r="B406" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C406" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A407">
-        <v>52121502</v>
+        <v>52121501</v>
       </c>
       <c r="B407" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C407" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A408">
-        <v>52551206</v>
+        <v>52121502</v>
       </c>
       <c r="B408" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C408" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A409">
-        <v>52551207</v>
+        <v>52551206</v>
       </c>
       <c r="B409" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C409" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A410">
-        <v>52551208</v>
+        <v>52551207</v>
       </c>
       <c r="B410" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C410" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A411">
-        <v>41011101</v>
+        <v>52551208</v>
       </c>
       <c r="B411" t="s">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C411" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A412">
-        <v>41051101</v>
+        <v>41011101</v>
       </c>
       <c r="B412" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C412" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A413">
-        <v>41051102</v>
+        <v>41051101</v>
       </c>
       <c r="B413" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C413" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A414">
-        <v>41051103</v>
+        <v>41051102</v>
       </c>
       <c r="B414" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C414" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A415">
-        <v>41051104</v>
+        <v>41051103</v>
       </c>
       <c r="B415" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C415" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A416">
-        <v>41051105</v>
+        <v>41051104</v>
       </c>
       <c r="B416" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C416" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A417">
-        <v>41051106</v>
+        <v>41051105</v>
       </c>
       <c r="B417" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C417" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A418">
-        <v>41101101</v>
+        <v>41051106</v>
       </c>
       <c r="B418" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C418" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A419">
-        <v>41101102</v>
+        <v>41101101</v>
       </c>
       <c r="B419" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C419" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A420">
-        <v>41101103</v>
+        <v>41101102</v>
       </c>
       <c r="B420" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C420" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A421">
-        <v>41101104</v>
+        <v>41101103</v>
       </c>
       <c r="B421" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C421" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A422">
-        <v>41101105</v>
+        <v>41101104</v>
       </c>
       <c r="B422" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C422" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A423">
-        <v>41101106</v>
+        <v>41101105</v>
       </c>
       <c r="B423" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C423" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A424">
-        <v>41101107</v>
+        <v>41101106</v>
       </c>
       <c r="B424" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C424" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A425">
-        <v>41101201</v>
+        <v>41101107</v>
       </c>
       <c r="B425" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C425" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A426">
-        <v>41101202</v>
+        <v>41101201</v>
       </c>
       <c r="B426" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C426" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A427">
-        <v>41101301</v>
+        <v>41101202</v>
       </c>
       <c r="B427" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C427" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A428">
-        <v>41101302</v>
+        <v>41101301</v>
       </c>
       <c r="B428" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C428" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A429">
-        <v>41101303</v>
+        <v>41101302</v>
       </c>
       <c r="B429" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C429" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A430">
-        <v>41101401</v>
+        <v>41101303</v>
       </c>
       <c r="B430" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C430" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A431">
-        <v>41101501</v>
+        <v>41101401</v>
       </c>
       <c r="B431" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C431" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A432">
-        <v>41101502</v>
+        <v>41101501</v>
       </c>
       <c r="B432" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C432" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A433">
-        <v>41101503</v>
+        <v>41101502</v>
       </c>
       <c r="B433" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C433" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A434">
-        <v>41101504</v>
+        <v>41101503</v>
       </c>
       <c r="B434" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C434" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A435">
-        <v>41101601</v>
+        <v>41101504</v>
       </c>
       <c r="B435" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C435" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A436">
-        <v>41101602</v>
+        <v>41101601</v>
       </c>
       <c r="B436" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C436" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A437">
-        <v>41101603</v>
+        <v>41101602</v>
       </c>
       <c r="B437" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C437" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A438">
-        <v>41101604</v>
+        <v>41101603</v>
       </c>
       <c r="B438" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C438" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A439">
-        <v>41101697</v>
+        <v>41101604</v>
       </c>
       <c r="B439" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C439" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A440">
-        <v>41101698</v>
+        <v>41101697</v>
       </c>
       <c r="B440" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C440" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A441">
-        <v>41101699</v>
+        <v>41101698</v>
       </c>
       <c r="B441" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C441" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A442">
-        <v>41101701</v>
+        <v>41101699</v>
       </c>
       <c r="B442" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C442" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A443">
-        <v>41101801</v>
+        <v>41101701</v>
       </c>
       <c r="B443" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C443" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A444">
-        <v>41101802</v>
+        <v>41101801</v>
       </c>
       <c r="B444" t="s">
         <v>782</v>
       </c>
       <c r="C444" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A445">
-        <v>41102101</v>
+        <v>41101802</v>
       </c>
       <c r="B445" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C445" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A446">
-        <v>41102102</v>
+        <v>41102101</v>
       </c>
       <c r="B446" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C446" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A447">
-        <v>41102103</v>
+        <v>41102102</v>
       </c>
       <c r="B447" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C447" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A448">
-        <v>41102104</v>
+        <v>41102103</v>
       </c>
       <c r="B448" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C448" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A449">
-        <v>41102105</v>
+        <v>41102104</v>
       </c>
       <c r="B449" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C449" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A450">
-        <v>41102106</v>
+        <v>41102105</v>
       </c>
       <c r="B450" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C450" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A451">
-        <v>41102107</v>
+        <v>41102106</v>
       </c>
       <c r="B451" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C451" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A452">
-        <v>41102108</v>
+        <v>41102107</v>
       </c>
       <c r="B452" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C452" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A453">
-        <v>41102109</v>
+        <v>41102108</v>
       </c>
       <c r="B453" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C453" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A454">
-        <v>41102110</v>
+        <v>41102109</v>
       </c>
       <c r="B454" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C454" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A455">
-        <v>41102111</v>
+        <v>41102110</v>
       </c>
       <c r="B455" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C455" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A456">
-        <v>41102113</v>
+        <v>41102111</v>
       </c>
       <c r="B456" t="s">
         <v>793</v>
       </c>
       <c r="C456" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A457">
-        <v>41102201</v>
+        <v>41102113</v>
       </c>
       <c r="B457" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C457" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A458">
-        <v>41102202</v>
+        <v>41102201</v>
       </c>
       <c r="B458" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C458" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A459">
-        <v>41102203</v>
+        <v>41102202</v>
       </c>
       <c r="B459" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C459" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A460">
-        <v>41102204</v>
+        <v>41102203</v>
       </c>
       <c r="B460" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C460" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A461">
-        <v>41102205</v>
+        <v>41102204</v>
       </c>
       <c r="B461" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C461" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A462">
-        <v>41102301</v>
+        <v>41102205</v>
       </c>
       <c r="B462" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C462" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A463">
-        <v>41102302</v>
+        <v>41102301</v>
       </c>
       <c r="B463" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C463" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A464">
-        <v>41102304</v>
+        <v>41102302</v>
       </c>
       <c r="B464" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C464" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A465">
-        <v>41102305</v>
+        <v>41102304</v>
       </c>
       <c r="B465" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C465" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A466">
-        <v>41103101</v>
+        <v>41102305</v>
       </c>
       <c r="B466" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C466" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A467">
-        <v>41251201</v>
+        <v>41103101</v>
       </c>
       <c r="B467" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C467" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A468">
-        <v>41251202</v>
+        <v>41251201</v>
       </c>
       <c r="B468" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C468" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A469">
-        <v>41251203</v>
+        <v>41251202</v>
       </c>
       <c r="B469" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C469" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A470">
-        <v>41251401</v>
+        <v>41251203</v>
       </c>
       <c r="B470" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C470" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A471">
-        <v>41251402</v>
+        <v>41251401</v>
       </c>
       <c r="B471" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C471" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A472">
-        <v>42011201</v>
+        <v>41251402</v>
       </c>
       <c r="B472" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C472" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A473">
-        <v>42011202</v>
+        <v>42011201</v>
       </c>
       <c r="B473" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C473" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A474">
-        <v>42011203</v>
+        <v>42011202</v>
       </c>
       <c r="B474" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C474" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A475">
-        <v>42011204</v>
+        <v>42011203</v>
       </c>
       <c r="B475" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C475" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A476">
-        <v>42011301</v>
+        <v>42011204</v>
       </c>
       <c r="B476" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C476" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A477">
-        <v>42011302</v>
+        <v>42011301</v>
       </c>
       <c r="B477" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C477" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A478">
-        <v>42011401</v>
+        <v>42011302</v>
       </c>
       <c r="B478" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C478" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A479">
-        <v>42011599</v>
+        <v>42011401</v>
       </c>
       <c r="B479" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C479" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A480">
-        <v>42011601</v>
+        <v>42011599</v>
       </c>
       <c r="B480" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C480" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A481">
-        <v>42051101</v>
+        <v>42011601</v>
       </c>
       <c r="B481" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C481" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A482">
-        <v>42051102</v>
+        <v>42051101</v>
       </c>
       <c r="B482" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C482" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A483">
-        <v>42051199</v>
+        <v>42051102</v>
       </c>
       <c r="B483" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C483" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A484">
-        <v>43011101</v>
+        <v>42051199</v>
       </c>
       <c r="B484" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C484" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A485">
-        <v>44011101</v>
+        <v>43011101</v>
       </c>
       <c r="B485" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C485" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A486">
-        <v>49949901</v>
+        <v>44011101</v>
       </c>
       <c r="B486" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C486" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A487">
-        <v>49949902</v>
+        <v>49949901</v>
       </c>
       <c r="B487" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C487" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A488">
-        <v>49959901</v>
+        <v>49949902</v>
       </c>
       <c r="B488" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C488" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A489">
-        <v>49959902</v>
+        <v>49959901</v>
       </c>
       <c r="B489" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C489" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A490">
-        <v>49959903</v>
+        <v>49959902</v>
       </c>
       <c r="B490" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C490" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A491">
-        <v>49959904</v>
+        <v>49959903</v>
       </c>
       <c r="B491" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C491" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A492">
-        <v>49959905</v>
+        <v>49959904</v>
       </c>
       <c r="B492" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C492" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A493">
-        <v>49959906</v>
+        <v>49959905</v>
       </c>
       <c r="B493" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C493" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A494">
-        <v>49959907</v>
+        <v>49959906</v>
       </c>
       <c r="B494" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C494" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A495">
-        <v>49959908</v>
+        <v>49959907</v>
       </c>
       <c r="B495" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C495" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A496">
-        <v>49959909</v>
+        <v>49959908</v>
       </c>
       <c r="B496" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C496" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A497">
-        <v>49959910</v>
+        <v>49959909</v>
       </c>
       <c r="B497" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C497" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A498">
-        <v>49959911</v>
+        <v>49959910</v>
       </c>
       <c r="B498" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C498" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A499">
-        <v>49959912</v>
+        <v>49959911</v>
       </c>
       <c r="B499" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C499" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A500">
-        <v>49959913</v>
+        <v>49959912</v>
       </c>
       <c r="B500" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C500" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A501">
-        <v>49959914</v>
+        <v>49959913</v>
       </c>
       <c r="B501" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C501" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A502">
-        <v>49959997</v>
+        <v>49959914</v>
       </c>
       <c r="B502" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C502" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A503">
-        <v>49959998</v>
+        <v>49959997</v>
       </c>
       <c r="B503" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C503" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A504">
+        <v>49959998</v>
+      </c>
+      <c r="B504" t="s">
+        <v>840</v>
+      </c>
+      <c r="C504" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A505">
         <v>49959999</v>
       </c>
-      <c r="B504" t="s">
+      <c r="B505" t="s">
         <v>841</v>
       </c>
-      <c r="C504" t="s">
-        <v>844</v>
+      <c r="C505" t="s">
+        <v>851</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C504" xr:uid="{2A5820EA-EB21-4A41-8285-BAA1AA34B157}"/>
+  <autoFilter ref="A1:C505" xr:uid="{2A5820EA-EB21-4A41-8285-BAA1AA34B157}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8581,16 +8595,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>745</v>
@@ -8610,7 +8624,7 @@
         <v>740</v>
       </c>
       <c r="E2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -8627,7 +8641,7 @@
         <v>740</v>
       </c>
       <c r="E3" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -8644,7 +8658,7 @@
         <v>740</v>
       </c>
       <c r="E4" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -12309,7 +12323,7 @@
         <v>740</v>
       </c>
       <c r="E218" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
@@ -12326,7 +12340,7 @@
         <v>740</v>
       </c>
       <c r="E219" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.35">
@@ -12343,7 +12357,7 @@
         <v>740</v>
       </c>
       <c r="E220" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
@@ -12708,7 +12722,7 @@
         <v>740</v>
       </c>
       <c r="E241" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.35">
@@ -12725,7 +12739,7 @@
         <v>740</v>
       </c>
       <c r="E242" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.35">
@@ -12742,7 +12756,7 @@
         <v>740</v>
       </c>
       <c r="E243" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.35">
@@ -14320,7 +14334,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>81212102</v>
       </c>
@@ -14335,7 +14349,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>90212102</v>
       </c>
@@ -14350,7 +14364,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>80315101</v>
       </c>
@@ -14365,7 +14379,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>81315101</v>
       </c>
@@ -14380,7 +14394,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>90315101</v>
       </c>
@@ -14395,7 +14409,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>80212101</v>
       </c>
@@ -14410,7 +14424,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>81212101</v>
       </c>
@@ -14425,7 +14439,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>90212101</v>
       </c>
@@ -14440,7 +14454,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>80212104</v>
       </c>
@@ -14454,8 +14468,11 @@
       <c r="D345" s="2" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E345" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>81212104</v>
       </c>
@@ -14469,8 +14486,11 @@
       <c r="D346" s="2" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E346" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>90212104</v>
       </c>
@@ -14484,8 +14504,11 @@
       <c r="D347" s="2" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E347" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>80214101</v>
       </c>
@@ -14500,7 +14523,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>81214101</v>
       </c>
@@ -14515,7 +14538,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>90214101</v>
       </c>
@@ -14530,7 +14553,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>80213102</v>
       </c>
@@ -14545,7 +14568,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>81213102</v>
       </c>
@@ -15015,7 +15038,7 @@
         <v>231</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D380" s="2" t="s">
         <v>740</v>
@@ -15029,7 +15052,7 @@
         <v>231</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D381" s="2" t="s">
         <v>740</v>
@@ -15043,7 +15066,7 @@
         <v>231</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>740</v>
